--- a/www/download/IND.labour_force_value.s.mv.rpO1.xlsx
+++ b/www/download/IND.labour_force_value.s.mv.rpO1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3406692.542</t>
+          <t>3406692542390.24</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3443950.853</t>
+          <t>3443950853361.07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3502570.368</t>
+          <t>3502570368453.55</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3494712.538</t>
+          <t>3494712537586.07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4022014.812</t>
+          <t>4022014811843.6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4369572.776</t>
+          <t>4369572776106.21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4354272.782</t>
+          <t>4354272781821.68</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4643222.008</t>
+          <t>4643222008313.26</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>5628122.569</t>
+          <t>5628122569122.84</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>5662380.105</t>
+          <t>5662380104737.83</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>5626936.56</t>
+          <t>5626936559851.02</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>5200732.69</t>
+          <t>5200732690173.88</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>4695086.619</t>
+          <t>4695086619007.54</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>3882982.963</t>
+          <t>3882982962721.37</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>3680980.399</t>
+          <t>3680980398900.06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2296484.361</t>
+          <t>2296484361031.34</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1982474.392</t>
+          <t>1982474391955.54</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1797016.581</t>
+          <t>1797016581322.2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2038627.793</t>
+          <t>2038627792776.02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2151444.868</t>
+          <t>2151444868146.95</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2182296.579</t>
+          <t>2182296578503.56</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2303111.157</t>
+          <t>2303111156660.22</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2380452.389</t>
+          <t>2380452389327.19</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2760857.878</t>
+          <t>2760857877896.88</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2558018.672</t>
+          <t>2558018672165.52</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2358144.652</t>
+          <t>2358144651946.93</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2132619.443</t>
+          <t>2132619442514.89</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>1831757.687</t>
+          <t>1831757687206.4</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1553846.178</t>
+          <t>1553846177837.44</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1434100.344</t>
+          <t>1434100343792.44</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2615773.492</t>
+          <t>2615773491874.11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2271167.716</t>
+          <t>2271167716336.18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2102062.245</t>
+          <t>2102062244794.27</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2380388.614</t>
+          <t>2380388613794.54</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2554813.43</t>
+          <t>2554813430315.02</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2623307.72</t>
+          <t>2623307720036.08</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2869144.376</t>
+          <t>2869144376117.96</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3027601.372</t>
+          <t>3027601371843.13</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>3500800.128</t>
+          <t>3500800127861.64</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>3268287.781</t>
+          <t>3268287780655.69</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>3005879.928</t>
+          <t>3005879927855.32</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2718032.711</t>
+          <t>2718032710831.93</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2337014.99</t>
+          <t>2337014989834.13</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1975811.475</t>
+          <t>1975811475018.77</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1839983.12</t>
+          <t>1839983120499.48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>98494.087</t>
+          <t>98494086679.7543</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>80599.367</t>
+          <t>80599367066.3167</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>62559.871</t>
+          <t>62559871405.2066</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>90724.219</t>
+          <t>90724219499.1315</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>93723.106</t>
+          <t>93723105843.5039</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>96870.806</t>
+          <t>96870805748.8326</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>112405.233</t>
+          <t>112405233483.793</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>121291.065</t>
+          <t>121291065140.732</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>150145.782</t>
+          <t>150145781526.859</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>147278.229</t>
+          <t>147278228514.69</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>143932.434</t>
+          <t>143932434336.293</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>137802.252</t>
+          <t>137802252279.271</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>135994.118</t>
+          <t>135994117955.214</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>131778.398</t>
+          <t>131778397721.845</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>128961.088</t>
+          <t>128961087513.335</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5885499.047</t>
+          <t>5885499047264.33</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5747683.425</t>
+          <t>5747683425476.97</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5945861.682</t>
+          <t>5945861682224.38</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>6502112.235</t>
+          <t>6502112235336.28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4747740.589</t>
+          <t>4747740589294.4</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5777201.931</t>
+          <t>5777201931232.76</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5347184.516</t>
+          <t>5347184516245.87</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4729967.269</t>
+          <t>4729967269467.2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4740479.687</t>
+          <t>4740479687492.6</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4660167.068</t>
+          <t>4660167068447.37</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>5633113.306</t>
+          <t>5633113305632.8</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>6048846.082</t>
+          <t>6048846081952.43</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>5740414.412</t>
+          <t>5740414411917.62</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>5251999.032</t>
+          <t>5251999031858.24</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>5216380.58</t>
+          <t>5216380579671.79</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5474908.942</t>
+          <t>5474908941600.09</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5061761.817</t>
+          <t>5061761817195.75</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5413535.662</t>
+          <t>5413535661846.48</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5890447.937</t>
+          <t>5890447937228.83</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6616376.281</t>
+          <t>6616376281324.47</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8130868.127</t>
+          <t>8130868126580.59</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8708970.508</t>
+          <t>8708970508061.79</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8612743.886</t>
+          <t>8612743886091.66</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>9611157.026</t>
+          <t>9611157025911.87</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>9038052.313</t>
+          <t>9038052313339.36</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>9119003.109</t>
+          <t>9119003109300.54</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>8902197.545</t>
+          <t>8902197545485.1</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>7410866.979</t>
+          <t>7410866979403.69</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>5926318.805</t>
+          <t>5926318804684.15</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>5106924.241</t>
+          <t>5106924240524.41</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7138485.627</t>
+          <t>7138485627024.85</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7529324.581</t>
+          <t>7529324580784.61</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8523837.789</t>
+          <t>8523837789218.45</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>9953721.1</t>
+          <t>9953721099891.64</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>11013548.988</t>
+          <t>11013548988489.4</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>13443257.317</t>
+          <t>13443257317302.6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15567249.211</t>
+          <t>15567249211437</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16082366.664</t>
+          <t>16082366664196.4</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>16768810.702</t>
+          <t>16768810702113.4</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>16049153.594</t>
+          <t>16049153594490.7</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>16151673.207</t>
+          <t>16151673206733.2</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>16046792.319</t>
+          <t>16046792319491.6</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>14924477.999</t>
+          <t>14924477999210</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>14477915.73</t>
+          <t>14477915730223.3</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>15411386.759</t>
+          <t>15411386758799.9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>71936.418</t>
+          <t>71936418024.3562</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>66171.508</t>
+          <t>66171507744.0884</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>65856.933</t>
+          <t>65856933199.2303</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>76325.605</t>
+          <t>76325604758.0028</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>82558.826</t>
+          <t>82558825687.0731</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>87967.089</t>
+          <t>87967089401.2113</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>96737.564</t>
+          <t>96737564388.6956</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>106044.327</t>
+          <t>106044326595.754</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>131513.923</t>
+          <t>131513923083.861</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>127228.515</t>
+          <t>127228514989.476</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>121158.386</t>
+          <t>121158385540.791</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>111927.86</t>
+          <t>111927859519.754</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>96996.925</t>
+          <t>96996924587.6467</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>83754.868</t>
+          <t>83754868283.7115</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>78274.066</t>
+          <t>78274066285.4785</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>326921.397</t>
+          <t>326921397242.465</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>437647.25</t>
+          <t>437647249723.173</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>417553.182</t>
+          <t>417553182063.22</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>479332.152</t>
+          <t>479332151614.755</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>491504.751</t>
+          <t>491504751352.933</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>528190.826</t>
+          <t>528190825876.056</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>618196.587</t>
+          <t>618196587113.804</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>742648.665</t>
+          <t>742648665358.756</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>865043.211</t>
+          <t>865043211334.123</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>835826.48</t>
+          <t>835826479898.748</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>851409.022</t>
+          <t>851409022498.898</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>834117.804</t>
+          <t>834117803561.901</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>761932.864</t>
+          <t>761932863954.271</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>727416.786</t>
+          <t>727416785725.565</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>612705.412</t>
+          <t>612705412311.478</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>24460025.09</t>
+          <t>24460025090457.2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>21089896.593</t>
+          <t>21089896593413.9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18888096.319</t>
+          <t>18888096318943.2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>21106496.984</t>
+          <t>21106496984278.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22084790.129</t>
+          <t>22084790129115.8</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>22500970.851</t>
+          <t>22500970850910.6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>23741821.119</t>
+          <t>23741821119334.5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>24283764.329</t>
+          <t>24283764328625.1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>27658951.806</t>
+          <t>27658951805536.9</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>25236579.619</t>
+          <t>25236579619315.6</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>22311565.823</t>
+          <t>22311565823461.2</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>19596065.519</t>
+          <t>19596065519304.5</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>16438735.372</t>
+          <t>16438735371564.6</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>13745478.458</t>
+          <t>13745478458000.7</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>12804444.052</t>
+          <t>12804444051914.3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1704013.754</t>
+          <t>1704013753864.56</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1555500.486</t>
+          <t>1555500485921.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1471819.429</t>
+          <t>1471819429446.59</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1705320.08</t>
+          <t>1705320079911.61</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1828471.518</t>
+          <t>1828471517670.93</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1866716.114</t>
+          <t>1866716113910.86</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2036474.268</t>
+          <t>2036474268399.42</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2145680.802</t>
+          <t>2145680802026.25</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2501919.589</t>
+          <t>2501919589318.69</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2340146.706</t>
+          <t>2340146706206.34</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2181925.755</t>
+          <t>2181925754684.27</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1990620.798</t>
+          <t>1990620798161.56</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>1737109.976</t>
+          <t>1737109976325.59</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>1465095.568</t>
+          <t>1465095567599.61</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1360870.07</t>
+          <t>1360870069771.98</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5235735.503</t>
+          <t>5235735502581.73</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4911912.967</t>
+          <t>4911912966772.59</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4704040.021</t>
+          <t>4704040020629.15</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>5466865.26</t>
+          <t>5466865259695.77</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>5983504.886</t>
+          <t>5983504886139.82</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6376071.68</t>
+          <t>6376071679936.63</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7081101.38</t>
+          <t>7081101379985.31</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>7637214.961</t>
+          <t>7637214960578.47</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>9240096.839</t>
+          <t>9240096838934.85</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>8896582.461</t>
+          <t>8896582461050.13</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>8500350.648</t>
+          <t>8500350648069.21</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>7917370.167</t>
+          <t>7917370167315.23</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>6993652.103</t>
+          <t>6993652103303.79</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>5950236.814</t>
+          <t>5950236814111.7</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>5366793.473</t>
+          <t>5366793473163.36</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>35493.293</t>
+          <t>35493293179.1104</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>38025.714</t>
+          <t>38025713998.0086</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>40364.371</t>
+          <t>40364370774.6285</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>48889.127</t>
+          <t>48889126795.7636</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>51723.719</t>
+          <t>51723719255.2577</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>56963.692</t>
+          <t>56963692474.5149</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>65471.696</t>
+          <t>65471695768.0156</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>73856.052</t>
+          <t>73856051627.1736</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>94211.584</t>
+          <t>94211584344.9163</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>95152.234</t>
+          <t>95152233569.6583</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>97548.546</t>
+          <t>97548546025.2576</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>101249.3</t>
+          <t>101249300226.166</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>102610.735</t>
+          <t>102610734842.769</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>93511.957</t>
+          <t>93511956922.6521</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>76119.234</t>
+          <t>76119233961.67</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1162310.105</t>
+          <t>1162310104633.41</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1032138.171</t>
+          <t>1032138170631.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>988818.573</t>
+          <t>988818572921.833</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1146748.238</t>
+          <t>1146748237548.99</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1222764.64</t>
+          <t>1222764639735.58</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1274189.022</t>
+          <t>1274189021598.1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1406014.575</t>
+          <t>1406014575436.83</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1471480.765</t>
+          <t>1471480764766.08</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1719186.532</t>
+          <t>1719186531575.84</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1625841.783</t>
+          <t>1625841783453.87</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1521978.518</t>
+          <t>1521978518016.63</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1374361.165</t>
+          <t>1374361164598.14</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1190049.742</t>
+          <t>1190049742033.23</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1017798.233</t>
+          <t>1017798233093.03</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>932547.427</t>
+          <t>932547426770.837</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14612837.108</t>
+          <t>14612837107906.7</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>13140067.769</t>
+          <t>13140067769145.2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12142305.587</t>
+          <t>12142305587366.9</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>13839342.053</t>
+          <t>13839342053202.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>14756674.89</t>
+          <t>14756674890282.2</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>15271069.086</t>
+          <t>15271069086000.3</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>16534057.979</t>
+          <t>16534057978593.4</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>17494173.238</t>
+          <t>17494173237977.5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>20441878.365</t>
+          <t>20441878364881.5</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>19223220.762</t>
+          <t>19223220762475.3</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>17723808.792</t>
+          <t>17723808792035</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>15968154.268</t>
+          <t>15968154268439</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>13568254.95</t>
+          <t>13568254950049.9</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>11286524.68</t>
+          <t>11286524680308.3</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>10392051.204</t>
+          <t>10392051204485.5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10933093.092</t>
+          <t>10933093092395.5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10153864.784</t>
+          <t>10153864784165.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>11636517.389</t>
+          <t>11636517389005.2</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14163884.418</t>
+          <t>14163884418225.2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>15670878.924</t>
+          <t>15670878923578</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>17842601.385</t>
+          <t>17842601385473.7</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>19191142.119</t>
+          <t>19191142119423.3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>20047810.008</t>
+          <t>20047810008002.6</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>21755120.354</t>
+          <t>21755120353613.3</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>21189283.188</t>
+          <t>21189283187640.8</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>19764632.657</t>
+          <t>19764632657062.3</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>18014258.295</t>
+          <t>18014258295139.3</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>15448917.742</t>
+          <t>15448917741890.8</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>10936625.843</t>
+          <t>10936625842836.3</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>9026515.845</t>
+          <t>9026515844833.96</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>753816.245</t>
+          <t>753816245089.19</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>707736.379</t>
+          <t>707736378864.734</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>728678.522</t>
+          <t>728678522163.187</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>824964.4</t>
+          <t>824964400377.66</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>922745.598</t>
+          <t>922745597744.788</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>937849.3</t>
+          <t>937849300134.203</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1012810.728</t>
+          <t>1012810727962.21</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1190316.486</t>
+          <t>1190316485821.94</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1464219.579</t>
+          <t>1464219579361.54</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1438423.486</t>
+          <t>1438423485636.28</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1353365.069</t>
+          <t>1353365069290.72</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1258251.35</t>
+          <t>1258251349886.56</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1119590.536</t>
+          <t>1119590535761.27</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>968128.795</t>
+          <t>968128795441.262</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>924239.787</t>
+          <t>924239787007.05</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>379458.373</t>
+          <t>379458372850.234</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>334891.352</t>
+          <t>334891351537.447</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>345330.766</t>
+          <t>345330765632.111</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>392164.266</t>
+          <t>392164265755.013</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>411009.23</t>
+          <t>411009230322.065</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>462268.534</t>
+          <t>462268534346.667</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>563765.664</t>
+          <t>563765663936.097</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>689566.246</t>
+          <t>689566245926.727</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>835698.627</t>
+          <t>835698626781.881</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>837424.294</t>
+          <t>837424293929.774</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>816872.419</t>
+          <t>816872419243.828</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>707151.14</t>
+          <t>707151139532.558</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>648678.5</t>
+          <t>648678500176.205</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>545942.373</t>
+          <t>545942373490.476</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>433244.136</t>
+          <t>433244136391.035</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1340043.052</t>
+          <t>1340043052003.65</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1380676.689</t>
+          <t>1380676688886.36</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1412365.127</t>
+          <t>1412365126952.66</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>593927.249</t>
+          <t>593927249460.57</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>957942.788</t>
+          <t>957942788346.528</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1153696.853</t>
+          <t>1153696852952.53</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1207750.066</t>
+          <t>1207750065801</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1410269.639</t>
+          <t>1410269639012.47</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1611069.923</t>
+          <t>1611069923052.45</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1406551.443</t>
+          <t>1406551443224.07</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1364898.874</t>
+          <t>1364898874066.51</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1558144.869</t>
+          <t>1558144868745.07</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1376656.209</t>
+          <t>1376656208500.82</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1213706.311</t>
+          <t>1213706310792.98</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1258336.275</t>
+          <t>1258336274905.87</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2217920.799</t>
+          <t>2217920798613.55</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1932505.853</t>
+          <t>1932505852837.46</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2302655.042</t>
+          <t>2302655042131.73</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2563985.105</t>
+          <t>2563985105494.44</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2853237.404</t>
+          <t>2853237404051.37</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3283772.219</t>
+          <t>3283772219469.61</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3605110.879</t>
+          <t>3605110879134.26</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>3585134.954</t>
+          <t>3585134954154.33</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>3937226.489</t>
+          <t>3937226489498.61</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>3751576.879</t>
+          <t>3751576878741.74</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>3887638.675</t>
+          <t>3887638675128.61</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>3702883.534</t>
+          <t>3702883534064.88</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>3428684.874</t>
+          <t>3428684874245.13</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2799543.91</t>
+          <t>2799543910122.75</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2852949.836</t>
+          <t>2852949836461.57</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>542159.985</t>
+          <t>542159985228.233</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>528948.034</t>
+          <t>528948033742.291</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>573937.589</t>
+          <t>573937588743.985</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>677513.325</t>
+          <t>677513325390.612</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>766276.465</t>
+          <t>766276465239.949</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>855317.086</t>
+          <t>855317086376.043</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>987128.763</t>
+          <t>987128762506.299</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1075208.213</t>
+          <t>1075208213095.28</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1319619.597</t>
+          <t>1319619597031.61</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1305264.219</t>
+          <t>1305264218907.41</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1303284.603</t>
+          <t>1303284602894.52</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1239261.355</t>
+          <t>1239261354675.67</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>1096755.495</t>
+          <t>1096755495007.47</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>939865.914</t>
+          <t>939865914009.29</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>789366.67</t>
+          <t>789366670440.958</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>8349318.833</t>
+          <t>8349318832805.69</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8394749.478</t>
+          <t>8394749477555.01</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>8201640.187</t>
+          <t>8201640187188.85</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>8869619.64</t>
+          <t>8869619639822.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>9333661.718</t>
+          <t>9333661717612.96</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>9546313.456</t>
+          <t>9546313456439.02</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10436208.233</t>
+          <t>10436208233015.2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>11092909.905</t>
+          <t>11092909904691.3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>13088558.115</t>
+          <t>13088558114822.5</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>12320872.401</t>
+          <t>12320872400562.4</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>11482804.841</t>
+          <t>11482804841045.6</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>10376969.769</t>
+          <t>10376969769205.4</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>8810707.409</t>
+          <t>8810707409125.12</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>7352652.211</t>
+          <t>7352652210772.7</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>6738934.136</t>
+          <t>6738934135971.36</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>49258964.422</t>
+          <t>49258964421636.1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>37932825.504</t>
+          <t>37932825503519.7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>35616254.269</t>
+          <t>35616254268871.8</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>36101347.666</t>
+          <t>36101347665550.4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>43111002.007</t>
+          <t>43111002006651.4</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>52090219.945</t>
+          <t>52090219944542.9</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>48898436.4</t>
+          <t>48898436399997.6</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>44488867.848</t>
+          <t>44488867847672.7</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>45155566.006</t>
+          <t>45155566005673.9</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>40527911.372</t>
+          <t>40527911371898.7</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>35683709.747</t>
+          <t>35683709746882.3</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>29609966.128</t>
+          <t>29609966128437.1</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>22194371.928</t>
+          <t>22194371927940.7</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>18439333.157</t>
+          <t>18439333157364.6</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>18216275.471</t>
+          <t>18216275471494.8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4469643.821</t>
+          <t>4469643820963.19</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4384898.787</t>
+          <t>4384898787091.88</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4125063.788</t>
+          <t>4125063787827.93</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2959924.824</t>
+          <t>2959924823768.49</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3919078.587</t>
+          <t>3919078586568.67</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5070522.204</t>
+          <t>5070522203823.43</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5196057.697</t>
+          <t>5196057697460.35</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>5700366.979</t>
+          <t>5700366979396.49</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>6213786.874</t>
+          <t>6213786874190.05</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>5751229.076</t>
+          <t>5751229075944.86</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>6147675.478</t>
+          <t>6147675478131.85</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>5976420.092</t>
+          <t>5976420091802.78</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>4914959.557</t>
+          <t>4914959557238.82</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3338471.861</t>
+          <t>3338471861277.03</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2883069.577</t>
+          <t>2883069577037.74</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>44945.212</t>
+          <t>44945211727.8596</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>51282.718</t>
+          <t>51282718061.4244</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>64710.81</t>
+          <t>64710809747.8179</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>85762.258</t>
+          <t>85762258242.4653</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>91953.126</t>
+          <t>91953125704.6673</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>99697.106</t>
+          <t>99697105712.1248</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>109403.076</t>
+          <t>109403075773.372</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>124425.119</t>
+          <t>124425119029.557</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>157097.46</t>
+          <t>157097459799.399</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>162019.08</t>
+          <t>162019080394.049</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>168444.017</t>
+          <t>168444017096.661</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>175163.777</t>
+          <t>175163777369.137</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>171603.01</t>
+          <t>171603009814.894</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>162001.989</t>
+          <t>162001989152.153</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>123139.061</t>
+          <t>123139060547.116</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>174761.309</t>
+          <t>174761309152.918</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>155936.509</t>
+          <t>155936508810.063</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>146894.152</t>
+          <t>146894152424.63</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>169893.431</t>
+          <t>169893431128.689</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>189617.304</t>
+          <t>189617304277.506</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>207516.034</t>
+          <t>207516033704.63</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>235630.519</t>
+          <t>235630518504.617</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>255033.159</t>
+          <t>255033158873.367</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>298474.155</t>
+          <t>298474155175.086</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>286922.779</t>
+          <t>286922779265.603</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>275137.968</t>
+          <t>275137967731.013</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>253232.523</t>
+          <t>253232522627.619</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>224712.902</t>
+          <t>224712901858.634</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>208026.797</t>
+          <t>208026796684.229</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>198709.347</t>
+          <t>198709346740.265</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>38975.17</t>
+          <t>38975170373.9637</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>41962.906</t>
+          <t>41962906355.4264</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>45405.819</t>
+          <t>45405819106.234</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>54036.548</t>
+          <t>54036547812.6367</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>62012.925</t>
+          <t>62012924629.9712</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>71503.86</t>
+          <t>71503860152.9333</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>77749.005</t>
+          <t>77749005459.7537</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>81392.645</t>
+          <t>81392644608.6701</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>95434.451</t>
+          <t>95434450604.0125</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>96479.225</t>
+          <t>96479225488.3726</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>106364.289</t>
+          <t>106364289278.934</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>118628.862</t>
+          <t>118628861837.181</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>137000.209</t>
+          <t>137000208885.96</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>130230.549</t>
+          <t>130230548696.011</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>88582.906</t>
+          <t>88582905765.021</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1748588.021</t>
+          <t>1748588021156.6</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1682045.256</t>
+          <t>1682045256240.21</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2144682.056</t>
+          <t>2144682056404.28</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2593933.213</t>
+          <t>2593933212732.17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3196933.453</t>
+          <t>3196933453216</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4390421.192</t>
+          <t>4390421191911.92</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5205571.251</t>
+          <t>5205571250859.14</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>5227658.842</t>
+          <t>5227658842011.04</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>4743810.884</t>
+          <t>4743810883687.61</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>4014378.197</t>
+          <t>4014378196677.66</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>3972753.891</t>
+          <t>3972753891260.23</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>3681526.466</t>
+          <t>3681526465817.02</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2948910.413</t>
+          <t>2948910412704.84</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2331999.565</t>
+          <t>2331999564925.21</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1843624.535</t>
+          <t>1843624534610.16</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>28995.288</t>
+          <t>28995288288.0907</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>27615.691</t>
+          <t>27615690722.4796</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>27553.634</t>
+          <t>27553634477.2155</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>32184.005</t>
+          <t>32184004611.8371</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>34882.65</t>
+          <t>34882650140.662</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>37780.261</t>
+          <t>37780261289.0325</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>42423.163</t>
+          <t>42423162828.298</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>44646.282</t>
+          <t>44646281878.3603</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>50513.126</t>
+          <t>50513126212.0568</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>47381.063</t>
+          <t>47381063010.1589</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>43231.549</t>
+          <t>43231548821.4027</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>39506.403</t>
+          <t>39506403150.8566</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>33845.301</t>
+          <t>33845300640.6042</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>31994.433</t>
+          <t>31994432867.1032</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>29301.066</t>
+          <t>29301066490.9404</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>3841095.85</t>
+          <t>3841095849573.39</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3406197.833</t>
+          <t>3406197833419.23</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3199765.172</t>
+          <t>3199765171635.69</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>3756401.622</t>
+          <t>3756401621571.63</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4108232.702</t>
+          <t>4108232702326.84</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4325992.706</t>
+          <t>4325992705517.84</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4810690.155</t>
+          <t>4810690154911.07</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>5134134.829</t>
+          <t>5134134828532.54</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>5998431.573</t>
+          <t>5998431572501.55</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>5567933.082</t>
+          <t>5567933082302</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>5022548.84</t>
+          <t>5022548840364.7</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>4515161.601</t>
+          <t>4515161601476.83</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>3903731.371</t>
+          <t>3903731371279.56</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>3297859.936</t>
+          <t>3297859935854.6</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>3082993.06</t>
+          <t>3082993060143.15</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>992612.445</t>
+          <t>992612445013.488</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1034165.849</t>
+          <t>1034165849321.21</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1087656.456</t>
+          <t>1087656456052.21</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1332215.52</t>
+          <t>1332215520000.25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1362891.226</t>
+          <t>1362891225996.76</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1526057.047</t>
+          <t>1526057046708.87</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1846284.545</t>
+          <t>1846284545190.45</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1764602.61</t>
+          <t>1764602609531.7</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1787547.845</t>
+          <t>1787547845313.2</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1639006.398</t>
+          <t>1639006398305.5</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1728116.824</t>
+          <t>1728116823945.85</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1648563.616</t>
+          <t>1648563616071.46</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1540883.897</t>
+          <t>1540883896642.18</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1514779.094</t>
+          <t>1514779094297.77</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1171854.965</t>
+          <t>1171854964634.59</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>978173.038</t>
+          <t>978173037582.883</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>922881.323</t>
+          <t>922881322558.948</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>910405.117</t>
+          <t>910405116663.332</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1070612.326</t>
+          <t>1070612325753.38</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1170810.077</t>
+          <t>1170810076781.5</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1246754.685</t>
+          <t>1246754684567.18</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1362071.233</t>
+          <t>1362071232867.45</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1454979.318</t>
+          <t>1454979318288.02</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1695183.262</t>
+          <t>1695183262345.67</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1592799.71</t>
+          <t>1592799709836.62</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1486819.5</t>
+          <t>1486819499615.9</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>1363992.117</t>
+          <t>1363992116604.7</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>1158174.775</t>
+          <t>1158174774782.11</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>961969.491</t>
+          <t>961969491141.803</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>883942.855</t>
+          <t>883942855150.266</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>256298.222</t>
+          <t>256298222337.596</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>227257.281</t>
+          <t>227257281287.182</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>193183.859</t>
+          <t>193183859441.325</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>293930.642</t>
+          <t>293930641625.105</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>247992.288</t>
+          <t>247992287752.794</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>330070.995</t>
+          <t>330070994567.747</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>398208.647</t>
+          <t>398208647419.751</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>413976.087</t>
+          <t>413976086952.469</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>481218.19</t>
+          <t>481218190150.848</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>500371.801</t>
+          <t>500371800671.821</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>615805.9</t>
+          <t>615805899759.129</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>639785.233</t>
+          <t>639785233305.315</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>675896.001</t>
+          <t>675896001289.997</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>657055.565</t>
+          <t>657055565250.227</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>494437.069</t>
+          <t>494437069277.265</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2712152.278</t>
+          <t>2712152277998.58</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2983521.521</t>
+          <t>2983521520622.38</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3056801.192</t>
+          <t>3056801191780.76</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2581172.37</t>
+          <t>2581172369962.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1586641.719</t>
+          <t>1586641718841.25</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2336605.631</t>
+          <t>2336605630551.32</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2962780.849</t>
+          <t>2962780849317.3</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>3358501.408</t>
+          <t>3358501407895.46</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>3881673.885</t>
+          <t>3881673884934.88</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>4284385.921</t>
+          <t>4284385920593.49</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>4794643.025</t>
+          <t>4794643025214.99</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>5322978.586</t>
+          <t>5322978586312.34</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>5343402.343</t>
+          <t>5343402343280.03</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>5121350.29</t>
+          <t>5121350290496.08</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>3771313.374</t>
+          <t>3771313374416.9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>105756.876</t>
+          <t>105756875914.438</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>106304.937</t>
+          <t>106304936568.784</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>116340.54</t>
+          <t>116340540101.052</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>133938.592</t>
+          <t>133938592088.209</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>124734.235</t>
+          <t>124734235158.814</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>141722.573</t>
+          <t>141722573151.666</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>151987.141</t>
+          <t>151987141008.8</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>169116.25</t>
+          <t>169116249576.492</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>215124.961</t>
+          <t>215124960559.842</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>215113.809</t>
+          <t>215113809263.966</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>220157.535</t>
+          <t>220157535285.476</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>217982.187</t>
+          <t>217982186885.826</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>217312.119</t>
+          <t>217312119298.366</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>208370.601</t>
+          <t>208370601052.496</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>198574.432</t>
+          <t>198574432115.603</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>208492.904</t>
+          <t>208492904238.922</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>183260.684</t>
+          <t>183260683818.553</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>176979.235</t>
+          <t>176979234656.172</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>203341.65</t>
+          <t>203341649535.067</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>218387.289</t>
+          <t>218387289421.533</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>227674.835</t>
+          <t>227674835030.974</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>250996.918</t>
+          <t>250996917689.696</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>269289.337</t>
+          <t>269289337145.692</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>319996.485</t>
+          <t>319996484686.958</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>307935.406</t>
+          <t>307935406455.238</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>289384.532</t>
+          <t>289384532487.733</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>267109.202</t>
+          <t>267109202304.985</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>239698.484</t>
+          <t>239698484100.151</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>211893.694</t>
+          <t>211893693961.075</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>193991.588</t>
+          <t>193991587842.345</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2388629.203</t>
+          <t>2388629202792.09</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2422876.348</t>
+          <t>2422876347521.64</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2260809.234</t>
+          <t>2260809233855.73</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2514062.684</t>
+          <t>2514062684262</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2663279.218</t>
+          <t>2663279218005.94</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3005248.408</t>
+          <t>3005248408271.49</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3038734.063</t>
+          <t>3038734062846.46</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>3204467.787</t>
+          <t>3204467786881.32</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>3769142.961</t>
+          <t>3769142961089.12</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>3530717.064</t>
+          <t>3530717064412.34</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>3198152.828</t>
+          <t>3198152827979.36</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2872044.47</t>
+          <t>2872044470485.51</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2525889.571</t>
+          <t>2525889571067.58</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>1997382.937</t>
+          <t>1997382936738.94</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>1639659.094</t>
+          <t>1639659094032.68</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>839030.571</t>
+          <t>839030571448.786</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>891283.511</t>
+          <t>891283510869.975</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1041131.515</t>
+          <t>1041131514513.86</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1179633.436</t>
+          <t>1179633435871.59</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1432163.032</t>
+          <t>1432163032015.57</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1619182.131</t>
+          <t>1619182130640.14</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1270067.683</t>
+          <t>1270067683463.44</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>1225404.818</t>
+          <t>1225404817887.54</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1500213.152</t>
+          <t>1500213152438.57</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1589675.934</t>
+          <t>1589675934457.36</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1767571.573</t>
+          <t>1767571573239.07</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1645535.679</t>
+          <t>1645535679020.59</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>1523636.928</t>
+          <t>1523636928008.68</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>1300167.176</t>
+          <t>1300167175503.85</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1055404.677</t>
+          <t>1055404676746.37</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2498954.032</t>
+          <t>2498954032496.86</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2356472.07</t>
+          <t>2356472070326.97</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2475905.908</t>
+          <t>2475905907988.91</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2468807.065</t>
+          <t>2468807065029.07</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2808472.755</t>
+          <t>2808472755043.57</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>3417217.467</t>
+          <t>3417217467296.71</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3340474.748</t>
+          <t>3340474747727.58</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>3136030.747</t>
+          <t>3136030746681.71</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>3073278.109</t>
+          <t>3073278109170.14</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2712409.514</t>
+          <t>2712409514017.67</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2629502.5</t>
+          <t>2629502499665.93</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2335334.42</t>
+          <t>2335334420293.31</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>1786300.034</t>
+          <t>1786300034342.61</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>1396572.366</t>
+          <t>1396572366409.3</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>1250183.122</t>
+          <t>1250183122225.5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>73765989.868</t>
+          <t>73765989867791.3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>69531570.672</t>
+          <t>69531570672181.9</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>75846603.855</t>
+          <t>75846603855267.1</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>90042999.41</t>
+          <t>90042999410192.1</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>101846852.025</t>
+          <t>101846852025005</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>124639494.822</t>
+          <t>124639494821868</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>138090077.404</t>
+          <t>138090077404166</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>136196347.274</t>
+          <t>136196347273741</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>135068612.485</t>
+          <t>135068612484776</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>117238628.746</t>
+          <t>117238628745582</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>110287107.819</t>
+          <t>110287107818719</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>99825100.618</t>
+          <t>99825100617768.5</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>78895916.294</t>
+          <t>78895916293871</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>60628940.924</t>
+          <t>60628940924130.8</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>57247692.942</t>
+          <t>57247692941658.7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>29714370.351</t>
+          <t>29714370350604.9</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>28209024.036</t>
+          <t>28209024035722.8</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>29341949.756</t>
+          <t>29341949755958.1</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>31384107.989</t>
+          <t>31384107989470.3</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>33775003.76</t>
+          <t>33775003760457.3</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>39989227.534</t>
+          <t>39989227533991.4</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>42647675.979</t>
+          <t>42647675979334.5</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>40390027.332</t>
+          <t>40390027331860.5</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>42510137.631</t>
+          <t>42510137631383.6</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>40457688.903</t>
+          <t>40457688902638.5</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>41373452.884</t>
+          <t>41373452884140.8</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>40384157.621</t>
+          <t>40384157621284</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>35182552.758</t>
+          <t>35182552757904.6</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>32138334.714</t>
+          <t>32138334713872.7</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>29158503.963</t>
+          <t>29158503962542</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>273107850.026</t>
+          <t>273107850025832</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>248373078.612</t>
+          <t>248373078612136</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>253145519.603</t>
+          <t>253145519603201</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>281264417.588</t>
+          <t>281264417587652</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>310568347.939</t>
+          <t>310568347939388</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>363440241.884</t>
+          <t>363440241884111</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>387781449.881</t>
+          <t>387781449881452</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>385282991.911</t>
+          <t>385282991911084</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>406839931.8</t>
+          <t>406839931799791</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>372536299.313</t>
+          <t>372536299313168</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>355132506.524</t>
+          <t>355132506524339</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>326829999.838</t>
+          <t>326829999837960</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>273513744.131</t>
+          <t>273513744130855</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>226403670.441</t>
+          <t>226403670441252</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>209997361.258</t>
+          <t>209997361257849</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>labour_force_value.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
